--- a/full_integration/assets/Train_Scheduling.xlsx
+++ b/full_integration/assets/Train_Scheduling.xlsx
@@ -1,33 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samar\OneDrive\Desktop\University of Pittsburgh\Year 4\SystemsAndProjectEng\Systems-Engineering-ECE1140\full_integration\assets\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8389063D-7AD6-4689-B373-07B849387376}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Red Line Scheduling" sheetId="1" r:id="rId1"/>
-    <sheet name="Green Line Scheduling" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="Red Line Scheduling"/>
+    <sheet r:id="rId2" sheetId="2" name="Green Line Scheduling"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -43,17 +26,18 @@
     <t>expected_arrival_times</t>
   </si>
   <si>
-    <t>INGLEWOOD, DORMONT, YARD</t>
+    <t>EDGEBROOK, YARD</t>
   </si>
   <si>
-    <t>7:30, 7:45, 8:00</t>
+    <t>7:30, 7:45</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -64,6 +48,12 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -95,29 +85,41 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -128,10 +130,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -169,71 +171,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -261,7 +263,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -284,11 +286,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -297,13 +299,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -313,7 +315,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -322,7 +324,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -331,7 +333,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -339,10 +341,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -407,24 +409,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -434,36 +438,37 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="7" width="35.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="31.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="2">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
+      <c r="A2" s="4">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="5" t="s">
         <v>4</v>
       </c>
     </row>

--- a/full_integration/assets/Train_Scheduling.xlsx
+++ b/full_integration/assets/Train_Scheduling.xlsx
@@ -1,16 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lao57_pitt_edu/Documents/CODE_folder/1140 code/Systems-Engineering-ECE1140/Track_Model_controller_integration/Systems-Engineering-ECE1140/full_integration/assets/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_75233AE577C69F4AB45C89C122FBC3CD7AE9D902" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{016D32F4-31CA-4ED6-A790-19E2C8885C43}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="2800" yWindow="2800" windowWidth="13700" windowHeight="12427" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Red Line Scheduling"/>
-    <sheet r:id="rId2" sheetId="2" name="Green Line Scheduling"/>
+    <sheet name="Red Line Scheduling" sheetId="1" r:id="rId1"/>
+    <sheet name="Green Line Scheduling" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -26,17 +32,16 @@
     <t>expected_arrival_times</t>
   </si>
   <si>
-    <t>EDGEBROOK, YARD</t>
+    <t>7:30, 7:45</t>
   </si>
   <si>
-    <t>7:30, 7:45</t>
+    <t>INGLEWOOD, YARD</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -85,41 +90,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -130,10 +129,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -171,71 +170,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -263,7 +262,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -286,11 +285,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -299,13 +298,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -315,7 +314,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -324,7 +323,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -333,7 +332,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -341,10 +340,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -409,26 +408,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="13.5859375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -438,38 +435,38 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" style="6" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="7" width="35.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="31.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.5859375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.5859375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.5859375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="19.5">
-      <c r="A2" s="4">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+      <c r="A2" s="3">
         <v>101</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="4" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
       </c>
     </row>
   </sheetData>

--- a/full_integration/assets/Train_Scheduling.xlsx
+++ b/full_integration/assets/Train_Scheduling.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lao57_pitt_edu/Documents/CODE_folder/1140 code/Systems-Engineering-ECE1140/Track_Model_controller_integration/Systems-Engineering-ECE1140/full_integration/assets/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samar\OneDrive\Desktop\University of Pittsburgh\Year 4\SystemsAndProjectEng\Systems-Engineering-ECE1140\full_integration\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_75233AE577C69F4AB45C89C122FBC3CD7AE9D902" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{016D32F4-31CA-4ED6-A790-19E2C8885C43}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F2FF7E-C2C4-4400-9614-8870773A8AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2800" yWindow="2800" windowWidth="13700" windowHeight="12427" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Red Line Scheduling" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <t>7:30, 7:45</t>
   </si>
   <si>
-    <t>INGLEWOOD, YARD</t>
+    <t>EDGEBROOK, YARD</t>
   </si>
 </sst>
 </file>
@@ -413,12 +413,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="3" width="13.5859375" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,14 +440,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="13.5859375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.5859375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.5859375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.54296875" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.54296875" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,7 +458,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="3">
         <v>101</v>
       </c>

--- a/full_integration/assets/Train_Scheduling.xlsx
+++ b/full_integration/assets/Train_Scheduling.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samar\OneDrive\Desktop\University of Pittsburgh\Year 4\SystemsAndProjectEng\Systems-Engineering-ECE1140\full_integration\assets\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lao57_pitt_edu/Documents/CODE_folder/1140 code/Systems-Engineering-ECE1140/Track_Model_controller_integration/Systems-Engineering-ECE1140/full_integration/assets/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F2FF7E-C2C4-4400-9614-8870773A8AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{98F2FF7E-C2C4-4400-9614-8870773A8AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{980B37B4-2031-4D79-9C6F-E7D1DC9FF4E4}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Red Line Scheduling" sheetId="1" r:id="rId1"/>
@@ -32,10 +32,10 @@
     <t>expected_arrival_times</t>
   </si>
   <si>
-    <t>7:30, 7:45</t>
+    <t>7:30, 7:45, 8:00</t>
   </si>
   <si>
-    <t>EDGEBROOK, YARD</t>
+    <t>DORMONT,GLENBURY, YARD</t>
   </si>
 </sst>
 </file>
@@ -122,6 +122,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -413,12 +417,12 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
+    <col min="1" max="3" width="13.52734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -440,14 +444,14 @@
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="1" max="1" width="13.54296875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.54296875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.54296875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="13.52734375" style="5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.52734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.52734375" style="2" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -458,7 +462,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
       <c r="A2" s="3">
         <v>101</v>
       </c>

--- a/full_integration/assets/Train_Scheduling.xlsx
+++ b/full_integration/assets/Train_Scheduling.xlsx
@@ -1,27 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://pitt-my.sharepoint.com/personal/lao57_pitt_edu/Documents/CODE_folder/1140 code/Systems-Engineering-ECE1140/Track_Model_controller_integration/Systems-Engineering-ECE1140/full_integration/assets/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{98F2FF7E-C2C4-4400-9614-8870773A8AAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{980B37B4-2031-4D79-9C6F-E7D1DC9FF4E4}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="15466" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Red Line Scheduling" sheetId="1" r:id="rId1"/>
-    <sheet name="Green Line Scheduling" sheetId="2" r:id="rId2"/>
+    <sheet r:id="rId1" sheetId="1" name="Red Line Scheduling"/>
+    <sheet r:id="rId2" sheetId="2" name="Green Line Scheduling"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
   <si>
     <t>Train ID</t>
   </si>
@@ -32,16 +26,23 @@
     <t>expected_arrival_times</t>
   </si>
   <si>
-    <t>7:30, 7:45, 8:00</t>
+    <t>GLENBURY, EDGEBROOK, YARD</t>
+  </si>
+  <si>
+    <t>8:00, 8:30, 9:00</t>
   </si>
   <si>
     <t>DORMONT,GLENBURY, YARD</t>
+  </si>
+  <si>
+    <t>7:30, 8:00, 8:30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
+  <numFmts count="0"/>
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -52,13 +53,13 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -90,42 +91,47 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+  <cellXfs count="10">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="general"/>
+    </xf>
+    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle xfId="0" builtinId="0" name="Normal"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -133,10 +139,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr lastClr="000000" val="windowText"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:sysClr lastClr="FFFFFF" val="window"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -174,71 +180,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Times New Roman" script="Arab"/>
+        <a:font typeface="Times New Roman" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="MoolBoran" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Times New Roman" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
+        <a:font typeface="맑은 고딕" script="Hang"/>
+        <a:font typeface="宋体" script="Hans"/>
+        <a:font typeface="新細明體" script="Hant"/>
+        <a:font typeface="Arial" script="Arab"/>
+        <a:font typeface="Arial" script="Hebr"/>
+        <a:font typeface="Tahoma" script="Thai"/>
+        <a:font typeface="Nyala" script="Ethi"/>
+        <a:font typeface="Vrinda" script="Beng"/>
+        <a:font typeface="Shruti" script="Gujr"/>
+        <a:font typeface="DaunPenh" script="Khmr"/>
+        <a:font typeface="Tunga" script="Knda"/>
+        <a:font typeface="Raavi" script="Guru"/>
+        <a:font typeface="Euphemia" script="Cans"/>
+        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
+        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
+        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
+        <a:font typeface="MV Boli" script="Thaa"/>
+        <a:font typeface="Mangal" script="Deva"/>
+        <a:font typeface="Gautami" script="Telu"/>
+        <a:font typeface="Latha" script="Taml"/>
+        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
+        <a:font typeface="Kalinga" script="Orya"/>
+        <a:font typeface="Kartika" script="Mlym"/>
+        <a:font typeface="DokChampa" script="Laoo"/>
+        <a:font typeface="Iskoola Pota" script="Sinh"/>
+        <a:font typeface="Mongolian Baiti" script="Mong"/>
+        <a:font typeface="Arial" script="Viet"/>
+        <a:font typeface="Microsoft Uighur" script="Uigh"/>
+        <a:font typeface="Sylfaen" script="Geor"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -266,7 +272,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -289,11 +295,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="16200000" scaled="1"/>
+          <a:lin scaled="1" ang="16200000"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -302,13 +308,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -318,7 +324,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -327,7 +333,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -336,7 +342,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -344,10 +350,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
+              <a:rot rev="0" lon="0" lat="0"/>
             </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
+            <a:lightRig dir="t" rig="threePt">
+              <a:rot rev="1200000" lon="0" lat="0"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -412,24 +418,26 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="3" width="13.52734375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A1" t="s">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
@@ -439,38 +447,49 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="13.52734375" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="35.52734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="31.52734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="2" max="2" style="8" width="35.57642857142857" customWidth="1" bestFit="1"/>
+    <col min="3" max="3" style="9" width="31.576428571428572" customWidth="1" bestFit="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.5">
+    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.5">
-      <c r="A2" s="3">
+    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
+      <c r="A2" s="4">
+        <v>201</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
+      <c r="A3" s="1">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="4" t="s">
-        <v>3</v>
+      <c r="B3" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>

--- a/full_integration/assets/Train_Scheduling.xlsx
+++ b/full_integration/assets/Train_Scheduling.xlsx
@@ -1,21 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion rupBuild="9303" lowestEdited="5" lastEdited="5" appName="xl"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\samar\OneDrive\Desktop\University of Pittsburgh\Year 4\SystemsAndProjectEng\Systems-Engineering-ECE1140\full_integration\assets\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CD03ECD-4974-4435-B086-1EA083627561}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="480" yWindow="60" windowWidth="18195" windowHeight="8505" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet r:id="rId1" sheetId="1" name="Red Line Scheduling"/>
-    <sheet r:id="rId2" sheetId="2" name="Green Line Scheduling"/>
+    <sheet name="Red Line Scheduling" sheetId="1" r:id="rId1"/>
+    <sheet name="Green Line Scheduling" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="19">
   <si>
     <t>Train ID</t>
   </si>
@@ -35,14 +41,49 @@
     <t>DORMONT,GLENBURY, YARD</t>
   </si>
   <si>
-    <t>7:30, 8:00, 8:30</t>
+    <t>8:30, 9:00, 9:30</t>
+  </si>
+  <si>
+    <t>9:00, 9:30, 10:00</t>
+  </si>
+  <si>
+    <t>DORMONT, EDGEBROOK, YARD</t>
+  </si>
+  <si>
+    <t>9:30, 10:00</t>
+  </si>
+  <si>
+    <t>DORMONT, YARD</t>
+  </si>
+  <si>
+    <t>GLENBURY, CENTRAL, YARD</t>
+  </si>
+  <si>
+    <t>DORMONT, PIONEER, YARD</t>
+  </si>
+  <si>
+    <t>7:30, 8:30</t>
+  </si>
+  <si>
+    <t>11:00, 11:30, 12:00</t>
+  </si>
+  <si>
+    <t>12:30, 13:00, 13:30</t>
+  </si>
+  <si>
+    <t>13:00, 13:30, 14:00</t>
+  </si>
+  <si>
+    <t>13:30, 14:00</t>
+  </si>
+  <si>
+    <t>10:00, 10:30, 11:30</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -91,44 +132,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0"/>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
+  <cellXfs count="6">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="2" applyFont="1" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf xfId="0" numFmtId="0" borderId="1" applyBorder="1" fontId="1" applyFont="1" fillId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf xfId="0" numFmtId="3" applyNumberFormat="1" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
-      <alignment horizontal="general"/>
-    </xf>
-    <xf xfId="0" numFmtId="0" borderId="0" fontId="0" fillId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle xfId="0" builtinId="0" name="Normal"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
-    <ext uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14ac:slicerStyles xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" defaultSlicerStyle="SlicerStyleLight1"/>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -139,10 +171,10 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr lastClr="000000" val="windowText"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr lastClr="FFFFFF" val="window"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
         <a:srgbClr val="0E2841"/>
@@ -180,71 +212,71 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Times New Roman" script="Arab"/>
-        <a:font typeface="Times New Roman" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="MoolBoran" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Times New Roman" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font typeface="ＭＳ Ｐゴシック" script="Jpan"/>
-        <a:font typeface="맑은 고딕" script="Hang"/>
-        <a:font typeface="宋体" script="Hans"/>
-        <a:font typeface="新細明體" script="Hant"/>
-        <a:font typeface="Arial" script="Arab"/>
-        <a:font typeface="Arial" script="Hebr"/>
-        <a:font typeface="Tahoma" script="Thai"/>
-        <a:font typeface="Nyala" script="Ethi"/>
-        <a:font typeface="Vrinda" script="Beng"/>
-        <a:font typeface="Shruti" script="Gujr"/>
-        <a:font typeface="DaunPenh" script="Khmr"/>
-        <a:font typeface="Tunga" script="Knda"/>
-        <a:font typeface="Raavi" script="Guru"/>
-        <a:font typeface="Euphemia" script="Cans"/>
-        <a:font typeface="Plantagenet Cherokee" script="Cher"/>
-        <a:font typeface="Microsoft Yi Baiti" script="Yiii"/>
-        <a:font typeface="Microsoft Himalaya" script="Tibt"/>
-        <a:font typeface="MV Boli" script="Thaa"/>
-        <a:font typeface="Mangal" script="Deva"/>
-        <a:font typeface="Gautami" script="Telu"/>
-        <a:font typeface="Latha" script="Taml"/>
-        <a:font typeface="Estrangelo Edessa" script="Syrc"/>
-        <a:font typeface="Kalinga" script="Orya"/>
-        <a:font typeface="Kartika" script="Mlym"/>
-        <a:font typeface="DokChampa" script="Laoo"/>
-        <a:font typeface="Iskoola Pota" script="Sinh"/>
-        <a:font typeface="Mongolian Baiti" script="Mong"/>
-        <a:font typeface="Arial" script="Viet"/>
-        <a:font typeface="Microsoft Uighur" script="Uigh"/>
-        <a:font typeface="Sylfaen" script="Geor"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -272,7 +304,7 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
@@ -295,11 +327,11 @@
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin scaled="1" ang="16200000"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="9525">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr">
               <a:shade val="9500"/>
@@ -308,13 +340,13 @@
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="25400">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
-        <a:ln algn="ctr" cmpd="sng" cap="flat" w="38100">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -324,7 +356,7 @@
       <a:effectStyleLst>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="38000"/>
               </a:srgbClr>
@@ -333,7 +365,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -342,7 +374,7 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw dir="5400000" rotWithShape="0" dist="23000" blurRad="40000">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
                 <a:alpha val="35000"/>
               </a:srgbClr>
@@ -350,10 +382,10 @@
           </a:effectLst>
           <a:scene3d>
             <a:camera prst="orthographicFront">
-              <a:rot rev="0" lon="0" lat="0"/>
+              <a:rot lat="0" lon="0" rev="0"/>
             </a:camera>
-            <a:lightRig dir="t" rig="threePt">
-              <a:rot rev="1200000" lon="0" lat="0"/>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
             </a:lightRig>
           </a:scene3d>
           <a:sp3d>
@@ -418,26 +450,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="8" width="13.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="3" width="13.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="18.75">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
@@ -447,49 +477,137 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" style="7" width="13.576428571428572" customWidth="1" bestFit="1"/>
-    <col min="2" max="2" style="8" width="35.57642857142857" customWidth="1" bestFit="1"/>
-    <col min="3" max="3" style="9" width="31.576428571428572" customWidth="1" bestFit="1"/>
+    <col min="1" max="1" width="13.54296875" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="35.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="31.54296875" style="4" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row x14ac:dyDescent="0.25" r="1" customHeight="1" ht="19.5">
+    <row r="1" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="2" customHeight="1" ht="18.75">
-      <c r="A2" s="4">
+    <row r="2" spans="1:3" ht="18.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
+        <v>1001</v>
+      </c>
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="19.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
+        <v>901</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
+        <v>801</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
+        <v>701</v>
+      </c>
+      <c r="B5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A6" s="1">
+        <v>601</v>
+      </c>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
+        <v>501</v>
+      </c>
+      <c r="B7" t="s">
+        <v>10</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
+        <v>401</v>
+      </c>
+      <c r="B8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
+        <v>301</v>
+      </c>
+      <c r="B9" t="s">
+        <v>8</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
         <v>201</v>
       </c>
-      <c r="B2" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="B10" t="s">
+        <v>11</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>4</v>
       </c>
     </row>
-    <row x14ac:dyDescent="0.25" r="3" customHeight="1" ht="19.5">
-      <c r="A3" s="1">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
         <v>101</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>6</v>
+      <c r="B11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
